--- a/employment_forms/023_pharmaceutical_industry_employment_form--employment_forms.xlsx
+++ b/employment_forms/023_pharmaceutical_industry_employment_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1103,8 +1103,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_'true'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 'true'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_'false'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': 'false'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time', 'value': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time', 'value': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'contract',_'value':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Contract', 'value': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'bachelor',_'value':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Bachelor', 'value': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'master',_'value':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Master', 'value': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'high_school',_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'High School', 'value': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'doctorate',_'value':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Doctorate', 'value': 'Doctorate'}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive', 'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
